--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415110</v>
+        <v>127415084</v>
       </c>
       <c r="B2" t="n">
         <v>98443</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809599</v>
+        <v>809722</v>
       </c>
       <c r="R2" t="n">
-        <v>7351945</v>
+        <v>7351819</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127415084</v>
+        <v>127415110</v>
       </c>
       <c r="B3" t="n">
         <v>98443</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809722</v>
+        <v>809599</v>
       </c>
       <c r="R3" t="n">
-        <v>7351819</v>
+        <v>7351945</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127415112</v>
+        <v>127415081</v>
       </c>
       <c r="B12" t="n">
         <v>98443</v>
@@ -1765,19 +1765,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Överstbyn, Nb</t>
+          <t>Gunnarsdjupträsk, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>809535</v>
+        <v>809724</v>
       </c>
       <c r="R12" t="n">
-        <v>7352091</v>
+        <v>7351822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127415081</v>
+        <v>127415112</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1871,19 +1871,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gunnarsdjupträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>809724</v>
+        <v>809535</v>
       </c>
       <c r="R13" t="n">
-        <v>7351822</v>
+        <v>7352091</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127415093</v>
+        <v>127415092</v>
       </c>
       <c r="B14" t="n">
         <v>98443</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>809653</v>
+        <v>809694</v>
       </c>
       <c r="R14" t="n">
-        <v>7351883</v>
+        <v>7351854</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127415092</v>
+        <v>127415093</v>
       </c>
       <c r="B15" t="n">
         <v>98443</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>809694</v>
+        <v>809653</v>
       </c>
       <c r="R15" t="n">
-        <v>7351854</v>
+        <v>7351883</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415108</v>
+        <v>127415087</v>
       </c>
       <c r="B16" t="n">
         <v>98443</v>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809696</v>
+        <v>809724</v>
       </c>
       <c r="R16" t="n">
-        <v>7352064</v>
+        <v>7351922</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127415094</v>
+        <v>127415108</v>
       </c>
       <c r="B17" t="n">
         <v>98443</v>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>809615</v>
+        <v>809696</v>
       </c>
       <c r="R17" t="n">
-        <v>7352015</v>
+        <v>7352064</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127415087</v>
+        <v>127415094</v>
       </c>
       <c r="B18" t="n">
         <v>98443</v>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>809724</v>
+        <v>809615</v>
       </c>
       <c r="R18" t="n">
-        <v>7351922</v>
+        <v>7352015</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127415097</v>
+        <v>127415077</v>
       </c>
       <c r="B19" t="n">
         <v>98443</v>
@@ -2507,19 +2507,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Överstbyn, Nb</t>
+          <t>Gunnarsdjupträsk, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>809498</v>
+        <v>809745</v>
       </c>
       <c r="R19" t="n">
-        <v>7352086</v>
+        <v>7351785</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127415077</v>
+        <v>127415097</v>
       </c>
       <c r="B20" t="n">
         <v>98443</v>
@@ -2613,19 +2613,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gunnarsdjupträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>809745</v>
+        <v>809498</v>
       </c>
       <c r="R20" t="n">
-        <v>7351785</v>
+        <v>7352086</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415084</v>
+        <v>127415110</v>
       </c>
       <c r="B2" t="n">
         <v>98443</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809722</v>
+        <v>809599</v>
       </c>
       <c r="R2" t="n">
-        <v>7351819</v>
+        <v>7351945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127415110</v>
+        <v>127415084</v>
       </c>
       <c r="B3" t="n">
         <v>98443</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809599</v>
+        <v>809722</v>
       </c>
       <c r="R3" t="n">
-        <v>7351945</v>
+        <v>7351819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415110</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415084</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415109</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415111</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127415096</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127415098</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127415101</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>127415089</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>127415091</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>127415085</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>127415081</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>127415112</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127415092</v>
+        <v>127415108</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>809694</v>
+        <v>809696</v>
       </c>
       <c r="R14" t="n">
-        <v>7351854</v>
+        <v>7352064</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127415093</v>
+        <v>127415094</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>809653</v>
+        <v>809615</v>
       </c>
       <c r="R15" t="n">
-        <v>7351883</v>
+        <v>7352015</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415087</v>
+        <v>127415092</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809724</v>
+        <v>809694</v>
       </c>
       <c r="R16" t="n">
-        <v>7351922</v>
+        <v>7351854</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127415108</v>
+        <v>127415093</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>809696</v>
+        <v>809653</v>
       </c>
       <c r="R17" t="n">
-        <v>7352064</v>
+        <v>7351883</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127415094</v>
+        <v>127415087</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>809615</v>
+        <v>809724</v>
       </c>
       <c r="R18" t="n">
-        <v>7352015</v>
+        <v>7351922</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2480,7 @@
         <v>127415077</v>
       </c>
       <c r="B19" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127415097</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415110</v>
+        <v>127415084</v>
       </c>
       <c r="B2" t="n">
         <v>98447</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809599</v>
+        <v>809722</v>
       </c>
       <c r="R2" t="n">
-        <v>7351945</v>
+        <v>7351819</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127415084</v>
+        <v>127415110</v>
       </c>
       <c r="B3" t="n">
         <v>98447</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809722</v>
+        <v>809599</v>
       </c>
       <c r="R3" t="n">
-        <v>7351819</v>
+        <v>7351945</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415084</v>
+        <v>127415110</v>
       </c>
       <c r="B2" t="n">
         <v>98447</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809722</v>
+        <v>809599</v>
       </c>
       <c r="R2" t="n">
-        <v>7351819</v>
+        <v>7351945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127415110</v>
+        <v>127415084</v>
       </c>
       <c r="B3" t="n">
         <v>98447</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809599</v>
+        <v>809722</v>
       </c>
       <c r="R3" t="n">
-        <v>7351945</v>
+        <v>7351819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415110</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415084</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415109</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415111</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127415096</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127415098</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127415101</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>127415089</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>127415091</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>127415085</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>127415081</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>127415112</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>127415108</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127415094</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127415092</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127415093</v>
       </c>
       <c r="B17" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>127415087</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>127415077</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127415097</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415110</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415084</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415109</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415111</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127415096</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127415098</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127415101</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>127415089</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>127415091</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>127415085</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>127415081</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>127415112</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>127415108</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127415094</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127415092</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127415093</v>
       </c>
       <c r="B17" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>127415087</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>127415077</v>
       </c>
       <c r="B19" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127415097</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127415108</v>
+        <v>127415094</v>
       </c>
       <c r="B14" t="n">
         <v>98450</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>809696</v>
+        <v>809615</v>
       </c>
       <c r="R14" t="n">
-        <v>7352064</v>
+        <v>7352015</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127415094</v>
+        <v>127415093</v>
       </c>
       <c r="B15" t="n">
         <v>98450</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>809615</v>
+        <v>809653</v>
       </c>
       <c r="R15" t="n">
-        <v>7352015</v>
+        <v>7351883</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415092</v>
+        <v>127415087</v>
       </c>
       <c r="B16" t="n">
         <v>98450</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809694</v>
+        <v>809724</v>
       </c>
       <c r="R16" t="n">
-        <v>7351854</v>
+        <v>7351922</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127415093</v>
+        <v>127415108</v>
       </c>
       <c r="B17" t="n">
         <v>98450</v>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>809653</v>
+        <v>809696</v>
       </c>
       <c r="R17" t="n">
-        <v>7351883</v>
+        <v>7352064</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127415087</v>
+        <v>127415092</v>
       </c>
       <c r="B18" t="n">
         <v>98450</v>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>809724</v>
+        <v>809694</v>
       </c>
       <c r="R18" t="n">
-        <v>7351922</v>
+        <v>7351854</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415110</v>
+        <v>127415084</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809599</v>
+        <v>809722</v>
       </c>
       <c r="R2" t="n">
-        <v>7351945</v>
+        <v>7351819</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127415084</v>
+        <v>127415110</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809722</v>
+        <v>809599</v>
       </c>
       <c r="R3" t="n">
-        <v>7351819</v>
+        <v>7351945</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>127415109</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415111</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127415096</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127415098</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127415101</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>127415089</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>127415091</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>127415085</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>127415081</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>127415112</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127415094</v>
+        <v>127415108</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>809615</v>
+        <v>809696</v>
       </c>
       <c r="R14" t="n">
-        <v>7352015</v>
+        <v>7352064</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127415093</v>
+        <v>127415094</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>809653</v>
+        <v>809615</v>
       </c>
       <c r="R15" t="n">
-        <v>7351883</v>
+        <v>7352015</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415087</v>
+        <v>127415092</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809724</v>
+        <v>809694</v>
       </c>
       <c r="R16" t="n">
-        <v>7351922</v>
+        <v>7351854</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127415108</v>
+        <v>127415093</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>809696</v>
+        <v>809653</v>
       </c>
       <c r="R17" t="n">
-        <v>7352064</v>
+        <v>7351883</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127415092</v>
+        <v>127415087</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>809694</v>
+        <v>809724</v>
       </c>
       <c r="R18" t="n">
-        <v>7351854</v>
+        <v>7351922</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2480,7 @@
         <v>127415077</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127415097</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415084</v>
+        <v>127415110</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809722</v>
+        <v>809599</v>
       </c>
       <c r="R2" t="n">
-        <v>7351819</v>
+        <v>7351945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127415110</v>
+        <v>127415084</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809599</v>
+        <v>809722</v>
       </c>
       <c r="R3" t="n">
-        <v>7351945</v>
+        <v>7351819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>127415109</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415111</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127415096</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127415098</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127415101</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>127415089</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>127415091</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>127415085</v>
       </c>
       <c r="B11" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>127415081</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>127415112</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>127415108</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127415094</v>
       </c>
       <c r="B15" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127415092</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127415093</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>127415087</v>
       </c>
       <c r="B18" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>127415077</v>
       </c>
       <c r="B19" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127415097</v>
       </c>
       <c r="B20" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415110</v>
+        <v>127415084</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809599</v>
+        <v>809722</v>
       </c>
       <c r="R2" t="n">
-        <v>7351945</v>
+        <v>7351819</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127415084</v>
+        <v>127415110</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809722</v>
+        <v>809599</v>
       </c>
       <c r="R3" t="n">
-        <v>7351819</v>
+        <v>7351945</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>127415109</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415111</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127415096</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127415098</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127415101</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>127415089</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>127415091</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>127415085</v>
       </c>
       <c r="B11" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>127415081</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>127415112</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127415108</v>
+        <v>127415093</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>809696</v>
+        <v>809653</v>
       </c>
       <c r="R14" t="n">
-        <v>7352064</v>
+        <v>7351883</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127415094</v>
+        <v>127415108</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>809615</v>
+        <v>809696</v>
       </c>
       <c r="R15" t="n">
-        <v>7352015</v>
+        <v>7352064</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415092</v>
+        <v>127415094</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809694</v>
+        <v>809615</v>
       </c>
       <c r="R16" t="n">
-        <v>7351854</v>
+        <v>7352015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127415093</v>
+        <v>127415092</v>
       </c>
       <c r="B17" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>809653</v>
+        <v>809694</v>
       </c>
       <c r="R17" t="n">
-        <v>7351883</v>
+        <v>7351854</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2374,7 +2374,7 @@
         <v>127415087</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>127415077</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127415097</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415084</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415110</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415109</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415111</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127415096</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127415098</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127415101</v>
+        <v>127415089</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>809686</v>
+        <v>809633</v>
       </c>
       <c r="R8" t="n">
-        <v>7351905</v>
+        <v>7351878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127415089</v>
+        <v>127415101</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>809633</v>
+        <v>809686</v>
       </c>
       <c r="R9" t="n">
-        <v>7351878</v>
+        <v>7351905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
         <v>127415091</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>127415085</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127415081</v>
+        <v>127415112</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,19 +1765,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gunnarsdjupträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>809724</v>
+        <v>809535</v>
       </c>
       <c r="R12" t="n">
-        <v>7351822</v>
+        <v>7352091</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127415112</v>
+        <v>127415081</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,19 +1871,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Överstbyn, Nb</t>
+          <t>Gunnarsdjupträsk, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>809535</v>
+        <v>809724</v>
       </c>
       <c r="R13" t="n">
-        <v>7352091</v>
+        <v>7351822</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127415093</v>
+        <v>127415108</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>809653</v>
+        <v>809696</v>
       </c>
       <c r="R14" t="n">
-        <v>7351883</v>
+        <v>7352064</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127415108</v>
+        <v>127415094</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>809696</v>
+        <v>809615</v>
       </c>
       <c r="R15" t="n">
-        <v>7352064</v>
+        <v>7352015</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415094</v>
+        <v>127415093</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809615</v>
+        <v>809653</v>
       </c>
       <c r="R16" t="n">
-        <v>7352015</v>
+        <v>7351883</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
         <v>127415092</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>127415087</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>127415077</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>127415097</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415084</v>
+        <v>127415110</v>
       </c>
       <c r="B2" t="n">
         <v>98468</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809722</v>
+        <v>809599</v>
       </c>
       <c r="R2" t="n">
-        <v>7351819</v>
+        <v>7351945</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127415110</v>
+        <v>127415084</v>
       </c>
       <c r="B3" t="n">
         <v>98468</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809599</v>
+        <v>809722</v>
       </c>
       <c r="R3" t="n">
-        <v>7351945</v>
+        <v>7351819</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127415089</v>
+        <v>127415101</v>
       </c>
       <c r="B8" t="n">
         <v>98468</v>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>809633</v>
+        <v>809686</v>
       </c>
       <c r="R8" t="n">
-        <v>7351878</v>
+        <v>7351905</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127415101</v>
+        <v>127415089</v>
       </c>
       <c r="B9" t="n">
         <v>98468</v>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>809686</v>
+        <v>809633</v>
       </c>
       <c r="R9" t="n">
-        <v>7351905</v>
+        <v>7351878</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127415112</v>
+        <v>127415081</v>
       </c>
       <c r="B12" t="n">
         <v>98468</v>
@@ -1765,19 +1765,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Överstbyn, Nb</t>
+          <t>Gunnarsdjupträsk, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>809535</v>
+        <v>809724</v>
       </c>
       <c r="R12" t="n">
-        <v>7352091</v>
+        <v>7351822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127415081</v>
+        <v>127415112</v>
       </c>
       <c r="B13" t="n">
         <v>98468</v>
@@ -1871,19 +1871,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gunnarsdjupträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>809724</v>
+        <v>809535</v>
       </c>
       <c r="R13" t="n">
-        <v>7351822</v>
+        <v>7352091</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415093</v>
+        <v>127415092</v>
       </c>
       <c r="B16" t="n">
         <v>98468</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809653</v>
+        <v>809694</v>
       </c>
       <c r="R16" t="n">
-        <v>7351883</v>
+        <v>7351854</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127415092</v>
+        <v>127415093</v>
       </c>
       <c r="B17" t="n">
         <v>98468</v>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>809694</v>
+        <v>809653</v>
       </c>
       <c r="R17" t="n">
-        <v>7351854</v>
+        <v>7351883</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415110</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415084</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415109</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415111</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127415096</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127415098</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>127415101</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>127415089</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>127415091</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>127415085</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>127415081</v>
       </c>
       <c r="B12" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>127415112</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>127415108</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127415094</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127415092</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127415093</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>127415087</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127415077</v>
+        <v>127415097</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gunnarsdjupträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>809745</v>
+        <v>809498</v>
       </c>
       <c r="R19" t="n">
-        <v>7351785</v>
+        <v>7352086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127415097</v>
+        <v>127415077</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,19 +2613,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Överstbyn, Nb</t>
+          <t>Gunnarsdjupträsk, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>809498</v>
+        <v>809745</v>
       </c>
       <c r="R20" t="n">
-        <v>7352086</v>
+        <v>7351785</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415110</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127415084</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127415109</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127415111</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>127415096</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>127415098</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127415101</v>
+        <v>127415089</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>809686</v>
+        <v>809633</v>
       </c>
       <c r="R8" t="n">
-        <v>7351905</v>
+        <v>7351878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127415089</v>
+        <v>127415101</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>809633</v>
+        <v>809686</v>
       </c>
       <c r="R9" t="n">
-        <v>7351878</v>
+        <v>7351905</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,7 +1526,7 @@
         <v>127415091</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>127415085</v>
       </c>
       <c r="B11" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>127415081</v>
       </c>
       <c r="B12" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>127415112</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>127415108</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>127415094</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>127415092</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127415093</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>127415087</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127415097</v>
+        <v>127415077</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Överstbyn, Nb</t>
+          <t>Gunnarsdjupträsk, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>809498</v>
+        <v>809745</v>
       </c>
       <c r="R19" t="n">
-        <v>7352086</v>
+        <v>7351785</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127415077</v>
+        <v>127415097</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,19 +2613,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gunnarsdjupträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>809745</v>
+        <v>809498</v>
       </c>
       <c r="R20" t="n">
-        <v>7351785</v>
+        <v>7352086</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 34696-2025 artfynd.xlsx
+++ b/artfynd/A 34696-2025 artfynd.xlsx
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127415108</v>
+        <v>127415087</v>
       </c>
       <c r="B14" t="n">
         <v>98470</v>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>809696</v>
+        <v>809724</v>
       </c>
       <c r="R14" t="n">
-        <v>7352064</v>
+        <v>7351922</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127415094</v>
+        <v>127415108</v>
       </c>
       <c r="B15" t="n">
         <v>98470</v>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>809615</v>
+        <v>809696</v>
       </c>
       <c r="R15" t="n">
-        <v>7352015</v>
+        <v>7352064</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127415092</v>
+        <v>127415094</v>
       </c>
       <c r="B16" t="n">
         <v>98470</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809694</v>
+        <v>809615</v>
       </c>
       <c r="R16" t="n">
-        <v>7351854</v>
+        <v>7352015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127415093</v>
+        <v>127415092</v>
       </c>
       <c r="B17" t="n">
         <v>98470</v>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>809653</v>
+        <v>809694</v>
       </c>
       <c r="R17" t="n">
-        <v>7351883</v>
+        <v>7351854</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127415087</v>
+        <v>127415093</v>
       </c>
       <c r="B18" t="n">
         <v>98470</v>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>809724</v>
+        <v>809653</v>
       </c>
       <c r="R18" t="n">
-        <v>7351922</v>
+        <v>7351883</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127415077</v>
+        <v>127415097</v>
       </c>
       <c r="B19" t="n">
         <v>98470</v>
@@ -2507,19 +2507,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gunnarsdjupträsk, Nb</t>
+          <t>Överstbyn, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>809745</v>
+        <v>809498</v>
       </c>
       <c r="R19" t="n">
-        <v>7351785</v>
+        <v>7352086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127415097</v>
+        <v>127415077</v>
       </c>
       <c r="B20" t="n">
         <v>98470</v>
@@ -2613,19 +2613,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Överstbyn, Nb</t>
+          <t>Gunnarsdjupträsk, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>809498</v>
+        <v>809745</v>
       </c>
       <c r="R20" t="n">
-        <v>7352086</v>
+        <v>7351785</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
